--- a/doc/基本設計/02_画面遷移図.xlsx
+++ b/doc/基本設計/02_画面遷移図.xlsx
@@ -145,17 +145,17 @@
       <charset val="1"/>
     </font>
     <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Noto Serif JP"/>
+      <family val="2"/>
+      <charset val="128"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="游ゴシック"/>
       <family val="0"/>
-      <charset val="128"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="Noto Serif JP"/>
-      <family val="2"/>
       <charset val="128"/>
     </font>
   </fonts>
@@ -306,13 +306,13 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>208440</xdr:colOff>
-      <xdr:row>27</xdr:row>
+      <xdr:row>23</xdr:row>
       <xdr:rowOff>72000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>216360</xdr:colOff>
-      <xdr:row>32</xdr:row>
+      <xdr:row>28</xdr:row>
       <xdr:rowOff>92880</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
@@ -322,7 +322,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2967480" y="4740480"/>
+          <a:off x="2967480" y="4039560"/>
           <a:ext cx="7920" cy="846360"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -348,14 +348,14 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>184320</xdr:colOff>
-      <xdr:row>14</xdr:row>
+      <xdr:row>10</xdr:row>
       <xdr:rowOff>164160</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>192240</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>133920</xdr:rowOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>134280</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -364,7 +364,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2943360" y="2604960"/>
+          <a:off x="2943360" y="1904040"/>
           <a:ext cx="7920" cy="846360"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -390,13 +390,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>727200</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>360</xdr:rowOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>90720</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>736560</xdr:colOff>
-      <xdr:row>28</xdr:row>
+      <xdr:colOff>729720</xdr:colOff>
+      <xdr:row>24</xdr:row>
       <xdr:rowOff>25560</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
@@ -406,8 +406,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm flipH="1">
-          <a:off x="1047960" y="2266200"/>
-          <a:ext cx="9360" cy="2590560"/>
+          <a:off x="1047960" y="1129680"/>
+          <a:ext cx="2520" cy="3025800"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -429,121 +429,6 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="absolute">
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>727920</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>151920</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>735840</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>122040</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp>
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="3" name="線 2"/>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1048680" y="840240"/>
-          <a:ext cx="7920" cy="846360"/>
-        </a:xfrm>
-        <a:prstGeom prst="line">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln w="0">
-          <a:solidFill>
-            <a:srgbClr val="3465a4"/>
-          </a:solidFill>
-          <a:tailEnd len="med" type="triangle" w="med"/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0"/>
-        <a:fillRef idx="0"/>
-        <a:effectRef idx="0"/>
-        <a:fontRef idx="minor"/>
-      </xdr:style>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>282960</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>134280</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>674640</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>10440</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp>
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="4" name="シェイプ 2"/>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="282960" y="1698840"/>
-          <a:ext cx="1525320" cy="577440"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="ffffff"/>
-        </a:solidFill>
-        <a:ln w="0">
-          <a:solidFill>
-            <a:srgbClr val="3465a4"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0"/>
-        <a:fillRef idx="0"/>
-        <a:effectRef idx="0"/>
-        <a:fontRef idx="minor"/>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr wrap="none" lIns="0" rIns="0" tIns="0" bIns="0" anchor="ctr">
-          <a:noAutofit/>
-        </a:bodyPr>
-        <a:p>
-          <a:pPr algn="ctr">
-            <a:lnSpc>
-              <a:spcPct val="100000"/>
-            </a:lnSpc>
-          </a:pPr>
-          <a:r>
-            <a:rPr b="0" lang="ja-JP" sz="1100" strike="noStrike" u="none">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:uFillTx/>
-              <a:latin typeface="游ゴシック"/>
-              <a:ea typeface="游ゴシック"/>
-            </a:rPr>
-            <a:t>ホーム画面</a:t>
-          </a:r>
-          <a:endParaRPr b="0" lang="en-US" sz="1100" strike="noStrike" u="none">
-            <a:effectLst/>
-            <a:uFillTx/>
-            <a:latin typeface="Noto Serif JP"/>
-          </a:endParaRPr>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="absolute">
-    <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>282960</xdr:colOff>
       <xdr:row>4</xdr:row>
@@ -551,19 +436,19 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>674640</xdr:colOff>
+      <xdr:colOff>673920</xdr:colOff>
       <xdr:row>7</xdr:row>
-      <xdr:rowOff>99720</xdr:rowOff>
+      <xdr:rowOff>99000</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
-        <xdr:cNvPr id="5" name="シェイプ 1"/>
+        <xdr:cNvPr id="3" name="シェイプ 1"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
           <a:off x="282960" y="736560"/>
-          <a:ext cx="1525320" cy="577440"/>
+          <a:ext cx="1524600" cy="576720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -619,24 +504,24 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>237960</xdr:colOff>
-      <xdr:row>14</xdr:row>
+      <xdr:row>10</xdr:row>
       <xdr:rowOff>51840</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>137520</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>103320</xdr:rowOff>
+      <xdr:colOff>136800</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>102600</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
-        <xdr:cNvPr id="6" name="シェイプ 3"/>
+        <xdr:cNvPr id="4" name="シェイプ 3"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2184120" y="2492640"/>
-          <a:ext cx="1525320" cy="577440"/>
+          <a:off x="2184120" y="1791720"/>
+          <a:ext cx="1524600" cy="576720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -692,24 +577,24 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>262080</xdr:colOff>
-      <xdr:row>26</xdr:row>
+      <xdr:row>22</xdr:row>
       <xdr:rowOff>56880</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>161640</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>146880</xdr:rowOff>
+      <xdr:colOff>160920</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>145800</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
-        <xdr:cNvPr id="7" name="シェイプ 4"/>
+        <xdr:cNvPr id="5" name="シェイプ 4"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2208240" y="4563000"/>
-          <a:ext cx="1525320" cy="577440"/>
+          <a:off x="2208240" y="3861720"/>
+          <a:ext cx="1524600" cy="576720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -765,24 +650,24 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>237960</xdr:colOff>
-      <xdr:row>19</xdr:row>
+      <xdr:row>15</xdr:row>
       <xdr:rowOff>138600</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>137520</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>27720</xdr:rowOff>
+      <xdr:colOff>136800</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>27000</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
-        <xdr:cNvPr id="8" name="シェイプ 6"/>
+        <xdr:cNvPr id="6" name="シェイプ 6"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2184120" y="3456000"/>
-          <a:ext cx="1525320" cy="577440"/>
+          <a:off x="2184120" y="2754720"/>
+          <a:ext cx="1524600" cy="576720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -838,24 +723,24 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>273600</xdr:colOff>
-      <xdr:row>32</xdr:row>
+      <xdr:row>28</xdr:row>
       <xdr:rowOff>86760</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>173160</xdr:colOff>
-      <xdr:row>36</xdr:row>
-      <xdr:rowOff>14040</xdr:rowOff>
+      <xdr:colOff>172440</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>13320</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
-        <xdr:cNvPr id="9" name="シェイプ 8"/>
+        <xdr:cNvPr id="7" name="シェイプ 8"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2219760" y="5580720"/>
-          <a:ext cx="1525320" cy="577440"/>
+          <a:off x="2219760" y="4879800"/>
+          <a:ext cx="1524600" cy="576720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -912,23 +797,23 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>719640</xdr:colOff>
-      <xdr:row>15</xdr:row>
+      <xdr:row>11</xdr:row>
       <xdr:rowOff>151920</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>231120</xdr:colOff>
-      <xdr:row>15</xdr:row>
+      <xdr:row>11</xdr:row>
       <xdr:rowOff>159480</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
-        <xdr:cNvPr id="10" name="線 1"/>
+        <xdr:cNvPr id="8" name="線 1"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1040400" y="2768040"/>
+          <a:off x="1040400" y="2067120"/>
           <a:ext cx="1136880" cy="7560"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -954,23 +839,23 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>732960</xdr:colOff>
-      <xdr:row>28</xdr:row>
+      <xdr:row>24</xdr:row>
       <xdr:rowOff>34920</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>222840</xdr:colOff>
-      <xdr:row>28</xdr:row>
+      <xdr:row>24</xdr:row>
       <xdr:rowOff>37800</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
-        <xdr:cNvPr id="11" name="線 4"/>
+        <xdr:cNvPr id="9" name="線 4"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1053720" y="4866120"/>
+          <a:off x="1053720" y="4164840"/>
           <a:ext cx="1115280" cy="2880"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -1172,7 +1057,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B1:D30"/>
+  <dimension ref="B1:D26"/>
   <sheetFormatPr defaultColWidth="10.4921875" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4.14"/>
@@ -1190,29 +1075,25 @@
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D10" s="4" t="s">
+        <v>1</v>
+      </c>
+    </row>
     <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D14" s="4" t="s">
-        <v>1</v>
-      </c>
-    </row>
+    <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D26" s="4" t="s">
+    <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D22" s="4" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
